--- a/Metadata.xlsx
+++ b/Metadata.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saber\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Program Files\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AEA9959-DD32-4BA6-BDF2-2AFB2795DD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="497" windowWidth="25920" windowHeight="16749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23145" windowHeight="9675" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="samples" sheetId="1" r:id="rId1"/>
     <sheet name="fingering_labels" sheetId="2" r:id="rId2"/>
     <sheet name="encoding_rules" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -53,7 +60,7 @@
     <t>sample_001</t>
   </si>
   <si>
-    <t>广陵散</t>
+    <t>Guangling San</t>
   </si>
   <si>
     <t>train</t>
@@ -62,19 +69,19 @@
     <t>sample_002</t>
   </si>
   <si>
-    <t>梅花三弄</t>
+    <t>Three Variations on Plum Blossom</t>
   </si>
   <si>
     <t>sample_003</t>
   </si>
   <si>
-    <t>平沙落雁</t>
+    <t>Wild Geese Descending on the Sandbank</t>
   </si>
   <si>
     <t>sample_004</t>
   </si>
   <si>
-    <t>阳关三叠</t>
+    <t>Three Variations on the Yangquan Pass</t>
   </si>
   <si>
     <t>sample_005</t>
@@ -101,257 +108,400 @@
     <t>sample_010</t>
   </si>
   <si>
+    <t>time_step</t>
+  </si>
+  <si>
     <t>fingering_label</t>
   </si>
   <si>
-    <t>右手食指挑七弦</t>
-  </si>
-  <si>
-    <t>左手大指按九徽</t>
-  </si>
-  <si>
-    <t>右手中指勾五弦</t>
-  </si>
-  <si>
-    <t>左手名指按十徽</t>
-  </si>
-  <si>
-    <t>右手食指抹六弦</t>
-  </si>
-  <si>
-    <t>左手大指按七徽</t>
-  </si>
-  <si>
-    <t>右手食指挑五弦</t>
-  </si>
-  <si>
-    <t>左手中指按十徽</t>
-  </si>
-  <si>
-    <t>右手无名指摘七弦</t>
-  </si>
-  <si>
-    <t>右手食指抹七弦</t>
-  </si>
-  <si>
-    <t>左手名指按九徽</t>
-  </si>
-  <si>
-    <t>右手中指勾六弦</t>
-  </si>
-  <si>
-    <t>右手食指抹五弦</t>
-  </si>
-  <si>
-    <t>右手中指勾七弦</t>
-  </si>
-  <si>
-    <t>右手食指挑六弦</t>
-  </si>
-  <si>
-    <t>右手托七弦</t>
-  </si>
-  <si>
-    <t>右手挑五弦</t>
-  </si>
-  <si>
-    <t>右手勾六弦</t>
-  </si>
-  <si>
-    <t>右手抹七弦</t>
-  </si>
-  <si>
-    <t>右手挑七弦</t>
-  </si>
-  <si>
-    <t>右手勾五弦</t>
-  </si>
-  <si>
-    <t>右手抹六弦</t>
-  </si>
-  <si>
-    <t>右手托六弦</t>
-  </si>
-  <si>
-    <t>右手勾七弦</t>
-  </si>
-  <si>
-    <t>右手托五弦</t>
-  </si>
-  <si>
-    <t>右手抹五弦</t>
-  </si>
-  <si>
-    <t>time_step</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>编码值</t>
-  </si>
-  <si>
-    <t>左手指法</t>
-  </si>
-  <si>
-    <t>徽位</t>
-  </si>
-  <si>
-    <t>右手指法</t>
-  </si>
-  <si>
-    <t>弦序</t>
-  </si>
-  <si>
-    <t>无/空</t>
-  </si>
-  <si>
-    <t>大指</t>
-  </si>
-  <si>
-    <t>一徽</t>
-  </si>
-  <si>
-    <t>挑</t>
-  </si>
-  <si>
-    <t>一弦</t>
-  </si>
-  <si>
-    <t>食指</t>
-  </si>
-  <si>
-    <t>二徽</t>
-  </si>
-  <si>
-    <t>勾</t>
-  </si>
-  <si>
-    <t>二弦</t>
-  </si>
-  <si>
-    <t>中指</t>
-  </si>
-  <si>
-    <t>三徽</t>
-  </si>
-  <si>
-    <t>抹</t>
-  </si>
-  <si>
-    <t>三弦</t>
-  </si>
-  <si>
-    <t>名指</t>
-  </si>
-  <si>
-    <t>四徽</t>
-  </si>
-  <si>
-    <t>剔</t>
-  </si>
-  <si>
-    <t>四弦</t>
-  </si>
-  <si>
-    <t>小指</t>
-  </si>
-  <si>
-    <t>五徽</t>
-  </si>
-  <si>
-    <t>托</t>
-  </si>
-  <si>
-    <t>五弦</t>
+    <t>Right hand index finger Tiao String 7</t>
+  </si>
+  <si>
+    <t>Left hand thumb Press Hui 9</t>
+  </si>
+  <si>
+    <t>Right hand middle finger Gou String 5</t>
+  </si>
+  <si>
+    <t>Left hand ring finger Press Hui 10</t>
+  </si>
+  <si>
+    <t>Right hand index finger Mo String 6</t>
+  </si>
+  <si>
+    <t>Left hand thumb Press Hui 7</t>
+  </si>
+  <si>
+    <t>Right hand index finger Tiao String 5</t>
+  </si>
+  <si>
+    <t>Left hand middle finger Press Hui 10</t>
+  </si>
+  <si>
+    <t>Right hand ring finger Zhai String 7</t>
+  </si>
+  <si>
+    <t>Right hand index finger Mo String 7</t>
+  </si>
+  <si>
+    <t>Left hand ring finger Press Hui 9</t>
+  </si>
+  <si>
+    <t>Right hand middle finger Gou String 6</t>
+  </si>
+  <si>
+    <t>Right hand index finger Mo String 5</t>
+  </si>
+  <si>
+    <t>Right hand middle finger Gou String 7</t>
+  </si>
+  <si>
+    <t>Right hand index finger Tiao String 6</t>
+  </si>
+  <si>
+    <t>Right hand Tuo String 7</t>
+  </si>
+  <si>
+    <t>Right hand Tiao String 5</t>
+  </si>
+  <si>
+    <t>Right hand Gou String 6</t>
+  </si>
+  <si>
+    <t>Right hand Mo String 7</t>
+  </si>
+  <si>
+    <t>Right hand Tiao String 7</t>
+  </si>
+  <si>
+    <t>Right hand Gou String 5</t>
+  </si>
+  <si>
+    <t>Right hand Mo String 6</t>
+  </si>
+  <si>
+    <t>Right hand Tuo String 6</t>
+  </si>
+  <si>
+    <t>Right hand Gou String 7</t>
+  </si>
+  <si>
+    <t>Right hand Tuo String 5</t>
+  </si>
+  <si>
+    <t>Right hand Mo String 5</t>
+  </si>
+  <si>
+    <t>encoding_value</t>
+  </si>
+  <si>
+    <t>left_hand_finger</t>
+  </si>
+  <si>
+    <t>hui_position</t>
+  </si>
+  <si>
+    <t>right_hand_technique</t>
+  </si>
+  <si>
+    <t>string_order</t>
+  </si>
+  <si>
+    <t>None/Empty</t>
+  </si>
+  <si>
+    <t>Thumb</t>
+  </si>
+  <si>
+    <t>Hui 1</t>
+  </si>
+  <si>
+    <t>Tiao</t>
+  </si>
+  <si>
+    <t>String 1</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>Hui 2</t>
+  </si>
+  <si>
+    <t>Gou</t>
+  </si>
+  <si>
+    <t>String 2</t>
+  </si>
+  <si>
+    <t>Middle</t>
+  </si>
+  <si>
+    <t>Hui 3</t>
+  </si>
+  <si>
+    <t>Mo</t>
+  </si>
+  <si>
+    <t>String 3</t>
+  </si>
+  <si>
+    <t>Ring</t>
+  </si>
+  <si>
+    <t>Hui 4</t>
+  </si>
+  <si>
+    <t>Ti</t>
+  </si>
+  <si>
+    <t>String 4</t>
+  </si>
+  <si>
+    <t>Little</t>
+  </si>
+  <si>
+    <t>Hui 5</t>
+  </si>
+  <si>
+    <t>Tuo</t>
+  </si>
+  <si>
+    <t>String 5</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>六徽</t>
-  </si>
-  <si>
-    <t>劈</t>
-  </si>
-  <si>
-    <t>六弦</t>
-  </si>
-  <si>
-    <t>七徽</t>
-  </si>
-  <si>
-    <t>摘</t>
-  </si>
-  <si>
-    <t>七弦</t>
-  </si>
-  <si>
-    <t>八徽</t>
-  </si>
-  <si>
-    <t>打</t>
-  </si>
-  <si>
-    <t>九徽</t>
-  </si>
-  <si>
-    <t>十徽</t>
-  </si>
-  <si>
-    <t>十一徽</t>
-  </si>
-  <si>
-    <t>十二徽</t>
-  </si>
-  <si>
-    <t>十三徽</t>
+    <t>Hui 6</t>
+  </si>
+  <si>
+    <t>Pi</t>
+  </si>
+  <si>
+    <t>String 6</t>
+  </si>
+  <si>
+    <t>Hui 7</t>
+  </si>
+  <si>
+    <t>Zhai</t>
+  </si>
+  <si>
+    <t>String 7</t>
+  </si>
+  <si>
+    <t>Hui 8</t>
+  </si>
+  <si>
+    <t>Da</t>
+  </si>
+  <si>
+    <t>Hui 9</t>
+  </si>
+  <si>
+    <t>Hui 10</t>
+  </si>
+  <si>
+    <t>Hui 11</t>
+  </si>
+  <si>
+    <t>Hui 12</t>
+  </si>
+  <si>
+    <t>Hui 13</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF0F1115"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,8 +514,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -375,53 +711,336 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -470,7 +1089,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -505,7 +1124,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -679,30 +1298,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="13.78515625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="12" style="6" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" style="6" customWidth="1"/>
-    <col min="4" max="4" width="8.78515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="12.35546875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="13.0703125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="13.7833333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="24.875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="22" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.78333333333333" style="3" customWidth="1"/>
+    <col min="5" max="5" width="12.3583333333333" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.0666666666667" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.425" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -725,14 +1339,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -748,14 +1362,14 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="3" ht="42.75" spans="1:7">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -771,14 +1385,14 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="4" ht="42.75" spans="1:7">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -794,14 +1408,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="5" ht="57" spans="1:7">
       <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -817,14 +1431,14 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -840,21 +1454,21 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="7" ht="42.75" spans="1:7">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="5">
-        <v>16.100000000000001</v>
+        <v>16.1</v>
       </c>
       <c r="F7" s="5">
         <v>193</v>
@@ -863,14 +1477,14 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="8" ht="42.75" spans="1:7">
       <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -886,14 +1500,14 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="9" ht="57" spans="1:7">
       <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -909,14 +1523,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7">
       <c r="A10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -932,14 +1546,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="11" ht="42.75" spans="1:7">
       <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -956,31 +1570,34 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1814F086-C06E-4195-9C60-C76CA1EC1152}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C266"/>
-  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="3" width="9.140625" style="3"/>
+    <col min="1" max="1" width="18.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="43" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="16.5" spans="1:3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+      <c r="C1" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -988,10 +1605,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -999,10 +1616,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1010,10 +1627,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1021,10 +1638,10 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -1032,10 +1649,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -1043,10 +1660,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1054,10 +1671,10 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -1065,10 +1682,10 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:3">
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
@@ -1076,10 +1693,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
@@ -1087,10 +1704,10 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:3">
       <c r="A12" s="2" t="s">
         <v>7</v>
       </c>
@@ -1098,10 +1715,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:3">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>
@@ -1109,10 +1726,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:3">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
@@ -1120,10 +1737,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
@@ -1131,10 +1748,10 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>7</v>
       </c>
@@ -1142,10 +1759,10 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:3">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -1153,10 +1770,10 @@
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="1:3">
       <c r="A18" s="2" t="s">
         <v>7</v>
       </c>
@@ -1164,10 +1781,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:3">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -1175,10 +1792,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:3">
       <c r="A20" s="2" t="s">
         <v>7</v>
       </c>
@@ -1186,10 +1803,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:3">
       <c r="A21" s="2" t="s">
         <v>7</v>
       </c>
@@ -1197,10 +1814,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:3">
       <c r="A22" s="2" t="s">
         <v>7</v>
       </c>
@@ -1208,10 +1825,10 @@
         <v>21</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:3">
       <c r="A23" s="2" t="s">
         <v>7</v>
       </c>
@@ -1219,10 +1836,10 @@
         <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:3">
       <c r="A24" s="2" t="s">
         <v>7</v>
       </c>
@@ -1230,10 +1847,10 @@
         <v>23</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:3">
       <c r="A25" s="2" t="s">
         <v>7</v>
       </c>
@@ -1241,10 +1858,10 @@
         <v>24</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:3">
       <c r="A26" s="2" t="s">
         <v>10</v>
       </c>
@@ -1252,10 +1869,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:3">
       <c r="A27" s="2" t="s">
         <v>10</v>
       </c>
@@ -1263,10 +1880,10 @@
         <v>2</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:3">
       <c r="A28" s="2" t="s">
         <v>10</v>
       </c>
@@ -1274,10 +1891,10 @@
         <v>3</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:3">
       <c r="A29" s="2" t="s">
         <v>10</v>
       </c>
@@ -1285,10 +1902,10 @@
         <v>4</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:3">
       <c r="A30" s="2" t="s">
         <v>10</v>
       </c>
@@ -1296,10 +1913,10 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="1:3">
       <c r="A31" s="2" t="s">
         <v>10</v>
       </c>
@@ -1307,10 +1924,10 @@
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="1:3">
       <c r="A32" s="2" t="s">
         <v>10</v>
       </c>
@@ -1318,10 +1935,10 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:3">
       <c r="A33" s="2" t="s">
         <v>10</v>
       </c>
@@ -1329,10 +1946,10 @@
         <v>8</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:3">
       <c r="A34" s="2" t="s">
         <v>10</v>
       </c>
@@ -1340,10 +1957,10 @@
         <v>9</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:3">
       <c r="A35" s="2" t="s">
         <v>10</v>
       </c>
@@ -1351,10 +1968,10 @@
         <v>10</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="1:3">
       <c r="A36" s="2" t="s">
         <v>10</v>
       </c>
@@ -1362,10 +1979,10 @@
         <v>11</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="1:3">
       <c r="A37" s="2" t="s">
         <v>10</v>
       </c>
@@ -1373,10 +1990,10 @@
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:3">
       <c r="A38" s="2" t="s">
         <v>10</v>
       </c>
@@ -1384,10 +2001,10 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:3">
       <c r="A39" s="2" t="s">
         <v>10</v>
       </c>
@@ -1395,10 +2012,10 @@
         <v>14</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="1:3">
       <c r="A40" s="2" t="s">
         <v>10</v>
       </c>
@@ -1406,10 +2023,10 @@
         <v>15</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:3">
       <c r="A41" s="2" t="s">
         <v>10</v>
       </c>
@@ -1417,10 +2034,10 @@
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:3">
       <c r="A42" s="2" t="s">
         <v>10</v>
       </c>
@@ -1428,10 +2045,10 @@
         <v>17</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:3">
       <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
@@ -1439,10 +2056,10 @@
         <v>18</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:3">
       <c r="A44" s="2" t="s">
         <v>10</v>
       </c>
@@ -1450,10 +2067,10 @@
         <v>19</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:3">
       <c r="A45" s="2" t="s">
         <v>10</v>
       </c>
@@ -1461,10 +2078,10 @@
         <v>20</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:3">
       <c r="A46" s="2" t="s">
         <v>10</v>
       </c>
@@ -1472,10 +2089,10 @@
         <v>21</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:3">
       <c r="A47" s="2" t="s">
         <v>10</v>
       </c>
@@ -1483,10 +2100,10 @@
         <v>22</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:3">
       <c r="A48" s="2" t="s">
         <v>10</v>
       </c>
@@ -1494,10 +2111,10 @@
         <v>23</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:3">
       <c r="A49" s="2" t="s">
         <v>10</v>
       </c>
@@ -1505,10 +2122,10 @@
         <v>24</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:3">
       <c r="A50" s="2" t="s">
         <v>10</v>
       </c>
@@ -1516,10 +2133,10 @@
         <v>25</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:3">
       <c r="A51" s="2" t="s">
         <v>10</v>
       </c>
@@ -1527,10 +2144,10 @@
         <v>26</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:3">
       <c r="A52" s="2" t="s">
         <v>10</v>
       </c>
@@ -1538,10 +2155,10 @@
         <v>27</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:3">
       <c r="A53" s="2" t="s">
         <v>10</v>
       </c>
@@ -1549,10 +2166,10 @@
         <v>28</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:3">
       <c r="A54" s="2" t="s">
         <v>10</v>
       </c>
@@ -1560,10 +2177,10 @@
         <v>29</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:3">
       <c r="A55" s="2" t="s">
         <v>10</v>
       </c>
@@ -1571,10 +2188,10 @@
         <v>30</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="1:3">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
@@ -1582,10 +2199,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:3">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -1593,10 +2210,10 @@
         <v>2</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:3">
       <c r="A58" s="2" t="s">
         <v>12</v>
       </c>
@@ -1604,10 +2221,10 @@
         <v>3</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:3">
       <c r="A59" s="2" t="s">
         <v>12</v>
       </c>
@@ -1615,10 +2232,10 @@
         <v>4</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:3">
       <c r="A60" s="2" t="s">
         <v>12</v>
       </c>
@@ -1626,10 +2243,10 @@
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:3">
       <c r="A61" s="2" t="s">
         <v>12</v>
       </c>
@@ -1637,10 +2254,10 @@
         <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:3">
       <c r="A62" s="2" t="s">
         <v>12</v>
       </c>
@@ -1648,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:3">
       <c r="A63" s="2" t="s">
         <v>12</v>
       </c>
@@ -1659,10 +2276,10 @@
         <v>8</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" spans="1:3">
       <c r="A64" s="2" t="s">
         <v>12</v>
       </c>
@@ -1670,10 +2287,10 @@
         <v>9</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" spans="1:3">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
@@ -1681,10 +2298,10 @@
         <v>10</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" ht="16.5" spans="1:3">
       <c r="A66" s="2" t="s">
         <v>12</v>
       </c>
@@ -1692,10 +2309,10 @@
         <v>11</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:3">
       <c r="A67" s="2" t="s">
         <v>12</v>
       </c>
@@ -1703,10 +2320,10 @@
         <v>12</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="1:3">
       <c r="A68" s="2" t="s">
         <v>12</v>
       </c>
@@ -1714,10 +2331,10 @@
         <v>13</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" spans="1:3">
       <c r="A69" s="2" t="s">
         <v>12</v>
       </c>
@@ -1725,10 +2342,10 @@
         <v>14</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="70" ht="16.5" spans="1:3">
       <c r="A70" s="2" t="s">
         <v>12</v>
       </c>
@@ -1736,10 +2353,10 @@
         <v>15</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="71" ht="16.5" spans="1:3">
       <c r="A71" s="2" t="s">
         <v>12</v>
       </c>
@@ -1747,10 +2364,10 @@
         <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" ht="16.5" spans="1:3">
       <c r="A72" s="2" t="s">
         <v>12</v>
       </c>
@@ -1758,10 +2375,10 @@
         <v>17</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="73" ht="16.5" spans="1:3">
       <c r="A73" s="2" t="s">
         <v>12</v>
       </c>
@@ -1769,10 +2386,10 @@
         <v>18</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" spans="1:3">
       <c r="A74" s="2" t="s">
         <v>12</v>
       </c>
@@ -1780,10 +2397,10 @@
         <v>19</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" spans="1:3">
       <c r="A75" s="2" t="s">
         <v>12</v>
       </c>
@@ -1791,10 +2408,10 @@
         <v>20</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" ht="16.5" spans="1:3">
       <c r="A76" s="2" t="s">
         <v>12</v>
       </c>
@@ -1802,10 +2419,10 @@
         <v>21</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" spans="1:3">
       <c r="A77" s="2" t="s">
         <v>12</v>
       </c>
@@ -1813,10 +2430,10 @@
         <v>22</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="78" ht="16.5" spans="1:3">
       <c r="A78" s="2" t="s">
         <v>12</v>
       </c>
@@ -1824,10 +2441,10 @@
         <v>23</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" ht="16.5" spans="1:3">
       <c r="A79" s="2" t="s">
         <v>12</v>
       </c>
@@ -1835,10 +2452,10 @@
         <v>24</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:3">
       <c r="A80" s="2" t="s">
         <v>12</v>
       </c>
@@ -1846,10 +2463,10 @@
         <v>25</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" spans="1:3">
       <c r="A81" s="2" t="s">
         <v>12</v>
       </c>
@@ -1857,10 +2474,10 @@
         <v>26</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="82" ht="16.5" spans="1:3">
       <c r="A82" s="2" t="s">
         <v>12</v>
       </c>
@@ -1868,10 +2485,10 @@
         <v>27</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" ht="16.5" spans="1:3">
       <c r="A83" s="2" t="s">
         <v>12</v>
       </c>
@@ -1879,10 +2496,10 @@
         <v>28</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="84" ht="16.5" spans="1:3">
       <c r="A84" s="2" t="s">
         <v>14</v>
       </c>
@@ -1890,10 +2507,10 @@
         <v>1</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="85" ht="16.5" spans="1:3">
       <c r="A85" s="2" t="s">
         <v>14</v>
       </c>
@@ -1901,10 +2518,10 @@
         <v>2</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="86" ht="16.5" spans="1:3">
       <c r="A86" s="2" t="s">
         <v>14</v>
       </c>
@@ -1912,10 +2529,10 @@
         <v>3</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="87" ht="16.5" spans="1:3">
       <c r="A87" s="2" t="s">
         <v>14</v>
       </c>
@@ -1923,10 +2540,10 @@
         <v>4</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="88" ht="16.5" spans="1:3">
       <c r="A88" s="2" t="s">
         <v>14</v>
       </c>
@@ -1934,10 +2551,10 @@
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="89" ht="16.5" spans="1:3">
       <c r="A89" s="2" t="s">
         <v>14</v>
       </c>
@@ -1945,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90" ht="16.5" spans="1:3">
       <c r="A90" s="2" t="s">
         <v>14</v>
       </c>
@@ -1956,10 +2573,10 @@
         <v>7</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="91" ht="16.5" spans="1:3">
       <c r="A91" s="2" t="s">
         <v>14</v>
       </c>
@@ -1967,10 +2584,10 @@
         <v>8</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="92" ht="16.5" spans="1:3">
       <c r="A92" s="2" t="s">
         <v>14</v>
       </c>
@@ -1978,10 +2595,10 @@
         <v>9</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93" ht="16.5" spans="1:3">
       <c r="A93" s="2" t="s">
         <v>14</v>
       </c>
@@ -1989,10 +2606,10 @@
         <v>10</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="94" ht="16.5" spans="1:3">
       <c r="A94" s="2" t="s">
         <v>14</v>
       </c>
@@ -2000,10 +2617,10 @@
         <v>11</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="95" ht="16.5" spans="1:3">
       <c r="A95" s="2" t="s">
         <v>14</v>
       </c>
@@ -2011,10 +2628,10 @@
         <v>12</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96" ht="16.5" spans="1:3">
       <c r="A96" s="2" t="s">
         <v>14</v>
       </c>
@@ -2022,10 +2639,10 @@
         <v>13</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="97" ht="16.5" spans="1:3">
       <c r="A97" s="2" t="s">
         <v>14</v>
       </c>
@@ -2033,10 +2650,10 @@
         <v>14</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="98" ht="16.5" spans="1:3">
       <c r="A98" s="2" t="s">
         <v>14</v>
       </c>
@@ -2044,10 +2661,10 @@
         <v>15</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="99" ht="16.5" spans="1:3">
       <c r="A99" s="2" t="s">
         <v>14</v>
       </c>
@@ -2055,10 +2672,10 @@
         <v>16</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="100" ht="16.5" spans="1:3">
       <c r="A100" s="2" t="s">
         <v>14</v>
       </c>
@@ -2066,10 +2683,10 @@
         <v>17</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="101" ht="16.5" spans="1:3">
       <c r="A101" s="2" t="s">
         <v>14</v>
       </c>
@@ -2077,10 +2694,10 @@
         <v>18</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="102" ht="16.5" spans="1:3">
       <c r="A102" s="2" t="s">
         <v>14</v>
       </c>
@@ -2088,10 +2705,10 @@
         <v>19</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="103" ht="16.5" spans="1:3">
       <c r="A103" s="2" t="s">
         <v>14</v>
       </c>
@@ -2099,10 +2716,10 @@
         <v>20</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="104" ht="16.5" spans="1:3">
       <c r="A104" s="2" t="s">
         <v>14</v>
       </c>
@@ -2110,10 +2727,10 @@
         <v>21</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="105" ht="16.5" spans="1:3">
       <c r="A105" s="2" t="s">
         <v>14</v>
       </c>
@@ -2121,10 +2738,10 @@
         <v>22</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="106" ht="16.5" spans="1:3">
       <c r="A106" s="2" t="s">
         <v>14</v>
       </c>
@@ -2132,10 +2749,10 @@
         <v>23</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="107" ht="16.5" spans="1:3">
       <c r="A107" s="2" t="s">
         <v>14</v>
       </c>
@@ -2143,10 +2760,10 @@
         <v>24</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="108" ht="16.5" spans="1:3">
       <c r="A108" s="2" t="s">
         <v>14</v>
       </c>
@@ -2154,10 +2771,10 @@
         <v>25</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="109" ht="16.5" spans="1:3">
       <c r="A109" s="2" t="s">
         <v>14</v>
       </c>
@@ -2165,10 +2782,10 @@
         <v>26</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="110" ht="16.5" spans="1:3">
       <c r="A110" s="2" t="s">
         <v>16</v>
       </c>
@@ -2176,10 +2793,10 @@
         <v>1</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="111" ht="16.5" spans="1:3">
       <c r="A111" s="2" t="s">
         <v>16</v>
       </c>
@@ -2187,10 +2804,10 @@
         <v>2</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="112" ht="16.5" spans="1:3">
       <c r="A112" s="2" t="s">
         <v>16</v>
       </c>
@@ -2198,10 +2815,10 @@
         <v>3</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="113" ht="16.5" spans="1:3">
       <c r="A113" s="2" t="s">
         <v>16</v>
       </c>
@@ -2209,10 +2826,10 @@
         <v>4</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="114" ht="16.5" spans="1:3">
       <c r="A114" s="2" t="s">
         <v>16</v>
       </c>
@@ -2220,10 +2837,10 @@
         <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="115" ht="16.5" spans="1:3">
       <c r="A115" s="2" t="s">
         <v>16</v>
       </c>
@@ -2231,10 +2848,10 @@
         <v>6</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="116" ht="16.5" spans="1:3">
       <c r="A116" s="2" t="s">
         <v>16</v>
       </c>
@@ -2242,10 +2859,10 @@
         <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="117" ht="16.5" spans="1:3">
       <c r="A117" s="2" t="s">
         <v>16</v>
       </c>
@@ -2253,10 +2870,10 @@
         <v>8</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="118" ht="16.5" spans="1:3">
       <c r="A118" s="2" t="s">
         <v>16</v>
       </c>
@@ -2264,10 +2881,10 @@
         <v>9</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="119" ht="16.5" spans="1:3">
       <c r="A119" s="2" t="s">
         <v>16</v>
       </c>
@@ -2275,10 +2892,10 @@
         <v>10</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="120" ht="16.5" spans="1:3">
       <c r="A120" s="2" t="s">
         <v>16</v>
       </c>
@@ -2286,10 +2903,10 @@
         <v>11</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="121" ht="16.5" spans="1:3">
       <c r="A121" s="2" t="s">
         <v>16</v>
       </c>
@@ -2297,10 +2914,10 @@
         <v>12</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="122" ht="16.5" spans="1:3">
       <c r="A122" s="2" t="s">
         <v>16</v>
       </c>
@@ -2308,10 +2925,10 @@
         <v>13</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="123" ht="16.5" spans="1:3">
       <c r="A123" s="2" t="s">
         <v>16</v>
       </c>
@@ -2319,10 +2936,10 @@
         <v>14</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="124" ht="16.5" spans="1:3">
       <c r="A124" s="2" t="s">
         <v>16</v>
       </c>
@@ -2330,10 +2947,10 @@
         <v>15</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="125" ht="16.5" spans="1:3">
       <c r="A125" s="2" t="s">
         <v>16</v>
       </c>
@@ -2341,10 +2958,10 @@
         <v>16</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="126" ht="16.5" spans="1:3">
       <c r="A126" s="2" t="s">
         <v>16</v>
       </c>
@@ -2352,10 +2969,10 @@
         <v>17</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="127" ht="16.5" spans="1:3">
       <c r="A127" s="2" t="s">
         <v>16</v>
       </c>
@@ -2363,10 +2980,10 @@
         <v>18</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="128" ht="16.5" spans="1:3">
       <c r="A128" s="2" t="s">
         <v>16</v>
       </c>
@@ -2374,10 +2991,10 @@
         <v>19</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="129" ht="16.5" spans="1:3">
       <c r="A129" s="2" t="s">
         <v>16</v>
       </c>
@@ -2385,10 +3002,10 @@
         <v>20</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="130" ht="16.5" spans="1:3">
       <c r="A130" s="2" t="s">
         <v>16</v>
       </c>
@@ -2396,10 +3013,10 @@
         <v>21</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="131" ht="16.5" spans="1:3">
       <c r="A131" s="2" t="s">
         <v>16</v>
       </c>
@@ -2407,10 +3024,10 @@
         <v>22</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="132" ht="16.5" spans="1:3">
       <c r="A132" s="2" t="s">
         <v>17</v>
       </c>
@@ -2418,10 +3035,10 @@
         <v>1</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="133" ht="16.5" spans="1:3">
       <c r="A133" s="2" t="s">
         <v>17</v>
       </c>
@@ -2429,10 +3046,10 @@
         <v>2</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="134" ht="16.5" spans="1:3">
       <c r="A134" s="2" t="s">
         <v>17</v>
       </c>
@@ -2440,10 +3057,10 @@
         <v>3</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="135" ht="16.5" spans="1:3">
       <c r="A135" s="2" t="s">
         <v>17</v>
       </c>
@@ -2451,10 +3068,10 @@
         <v>4</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="136" ht="16.5" spans="1:3">
       <c r="A136" s="2" t="s">
         <v>17</v>
       </c>
@@ -2462,10 +3079,10 @@
         <v>5</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="137" ht="16.5" spans="1:3">
       <c r="A137" s="2" t="s">
         <v>17</v>
       </c>
@@ -2473,10 +3090,10 @@
         <v>6</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="138" ht="16.5" spans="1:3">
       <c r="A138" s="2" t="s">
         <v>17</v>
       </c>
@@ -2484,10 +3101,10 @@
         <v>7</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="139" ht="16.5" spans="1:3">
       <c r="A139" s="2" t="s">
         <v>17</v>
       </c>
@@ -2495,10 +3112,10 @@
         <v>8</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="140" ht="16.5" spans="1:3">
       <c r="A140" s="2" t="s">
         <v>17</v>
       </c>
@@ -2506,10 +3123,10 @@
         <v>9</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="141" ht="16.5" spans="1:3">
       <c r="A141" s="2" t="s">
         <v>17</v>
       </c>
@@ -2517,10 +3134,10 @@
         <v>10</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="142" ht="16.5" spans="1:3">
       <c r="A142" s="2" t="s">
         <v>17</v>
       </c>
@@ -2528,10 +3145,10 @@
         <v>11</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="143" ht="16.5" spans="1:3">
       <c r="A143" s="2" t="s">
         <v>17</v>
       </c>
@@ -2539,10 +3156,10 @@
         <v>12</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="144" ht="16.5" spans="1:3">
       <c r="A144" s="2" t="s">
         <v>17</v>
       </c>
@@ -2550,10 +3167,10 @@
         <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="145" ht="16.5" spans="1:3">
       <c r="A145" s="2" t="s">
         <v>17</v>
       </c>
@@ -2561,10 +3178,10 @@
         <v>14</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="146" ht="16.5" spans="1:3">
       <c r="A146" s="2" t="s">
         <v>17</v>
       </c>
@@ -2572,10 +3189,10 @@
         <v>15</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="147" ht="16.5" spans="1:3">
       <c r="A147" s="2" t="s">
         <v>17</v>
       </c>
@@ -2583,10 +3200,10 @@
         <v>16</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="148" ht="16.5" spans="1:3">
       <c r="A148" s="2" t="s">
         <v>17</v>
       </c>
@@ -2594,10 +3211,10 @@
         <v>17</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="149" ht="16.5" spans="1:3">
       <c r="A149" s="2" t="s">
         <v>17</v>
       </c>
@@ -2605,10 +3222,10 @@
         <v>18</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="150" ht="16.5" spans="1:3">
       <c r="A150" s="2" t="s">
         <v>17</v>
       </c>
@@ -2616,10 +3233,10 @@
         <v>19</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="151" ht="16.5" spans="1:3">
       <c r="A151" s="2" t="s">
         <v>17</v>
       </c>
@@ -2627,10 +3244,10 @@
         <v>20</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="152" ht="16.5" spans="1:3">
       <c r="A152" s="2" t="s">
         <v>17</v>
       </c>
@@ -2638,10 +3255,10 @@
         <v>21</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="153" ht="16.5" spans="1:3">
       <c r="A153" s="2" t="s">
         <v>17</v>
       </c>
@@ -2649,10 +3266,10 @@
         <v>22</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="154" ht="16.5" spans="1:3">
       <c r="A154" s="2" t="s">
         <v>17</v>
       </c>
@@ -2660,10 +3277,10 @@
         <v>23</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="155" ht="16.5" spans="1:3">
       <c r="A155" s="2" t="s">
         <v>17</v>
       </c>
@@ -2671,10 +3288,10 @@
         <v>24</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="156" ht="16.5" spans="1:3">
       <c r="A156" s="2" t="s">
         <v>17</v>
       </c>
@@ -2682,10 +3299,10 @@
         <v>25</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="157" ht="16.5" spans="1:3">
       <c r="A157" s="2" t="s">
         <v>17</v>
       </c>
@@ -2693,10 +3310,10 @@
         <v>26</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="158" ht="16.5" spans="1:3">
       <c r="A158" s="2" t="s">
         <v>17</v>
       </c>
@@ -2704,10 +3321,10 @@
         <v>27</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="159" ht="16.5" spans="1:3">
       <c r="A159" s="2" t="s">
         <v>17</v>
       </c>
@@ -2715,10 +3332,10 @@
         <v>28</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="160" ht="16.5" spans="1:3">
       <c r="A160" s="2" t="s">
         <v>17</v>
       </c>
@@ -2726,10 +3343,10 @@
         <v>29</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="161" ht="16.5" spans="1:3">
       <c r="A161" s="2" t="s">
         <v>17</v>
       </c>
@@ -2737,10 +3354,10 @@
         <v>30</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="162" ht="16.5" spans="1:3">
       <c r="A162" s="2" t="s">
         <v>17</v>
       </c>
@@ -2748,10 +3365,10 @@
         <v>31</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="163" ht="16.5" spans="1:3">
       <c r="A163" s="2" t="s">
         <v>18</v>
       </c>
@@ -2759,10 +3376,10 @@
         <v>1</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="164" ht="16.5" spans="1:3">
       <c r="A164" s="2" t="s">
         <v>18</v>
       </c>
@@ -2770,10 +3387,10 @@
         <v>2</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="165" ht="16.5" spans="1:3">
       <c r="A165" s="2" t="s">
         <v>18</v>
       </c>
@@ -2781,10 +3398,10 @@
         <v>3</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="166" ht="16.5" spans="1:3">
       <c r="A166" s="2" t="s">
         <v>18</v>
       </c>
@@ -2792,10 +3409,10 @@
         <v>4</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="167" ht="16.5" spans="1:3">
       <c r="A167" s="2" t="s">
         <v>18</v>
       </c>
@@ -2803,10 +3420,10 @@
         <v>5</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="168" ht="16.5" spans="1:3">
       <c r="A168" s="2" t="s">
         <v>18</v>
       </c>
@@ -2814,10 +3431,10 @@
         <v>6</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="169" ht="16.5" spans="1:3">
       <c r="A169" s="2" t="s">
         <v>18</v>
       </c>
@@ -2825,10 +3442,10 @@
         <v>7</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="170" ht="16.5" spans="1:3">
       <c r="A170" s="2" t="s">
         <v>18</v>
       </c>
@@ -2836,10 +3453,10 @@
         <v>8</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="171" ht="16.5" spans="1:3">
       <c r="A171" s="2" t="s">
         <v>18</v>
       </c>
@@ -2847,10 +3464,10 @@
         <v>9</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="172" ht="16.5" spans="1:3">
       <c r="A172" s="2" t="s">
         <v>18</v>
       </c>
@@ -2858,10 +3475,10 @@
         <v>10</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="173" ht="16.5" spans="1:3">
       <c r="A173" s="2" t="s">
         <v>18</v>
       </c>
@@ -2869,10 +3486,10 @@
         <v>11</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="174" ht="16.5" spans="1:3">
       <c r="A174" s="2" t="s">
         <v>18</v>
       </c>
@@ -2880,10 +3497,10 @@
         <v>12</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="175" ht="16.5" spans="1:3">
       <c r="A175" s="2" t="s">
         <v>18</v>
       </c>
@@ -2891,10 +3508,10 @@
         <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="176" ht="16.5" spans="1:3">
       <c r="A176" s="2" t="s">
         <v>18</v>
       </c>
@@ -2902,10 +3519,10 @@
         <v>14</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="177" ht="16.5" spans="1:3">
       <c r="A177" s="2" t="s">
         <v>18</v>
       </c>
@@ -2913,10 +3530,10 @@
         <v>15</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="178" ht="16.5" spans="1:3">
       <c r="A178" s="2" t="s">
         <v>18</v>
       </c>
@@ -2924,10 +3541,10 @@
         <v>16</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="179" ht="16.5" spans="1:3">
       <c r="A179" s="2" t="s">
         <v>18</v>
       </c>
@@ -2935,10 +3552,10 @@
         <v>17</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="180" ht="16.5" spans="1:3">
       <c r="A180" s="2" t="s">
         <v>18</v>
       </c>
@@ -2946,10 +3563,10 @@
         <v>18</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="181" ht="16.5" spans="1:3">
       <c r="A181" s="2" t="s">
         <v>18</v>
       </c>
@@ -2957,10 +3574,10 @@
         <v>19</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="182" ht="16.5" spans="1:3">
       <c r="A182" s="2" t="s">
         <v>18</v>
       </c>
@@ -2968,10 +3585,10 @@
         <v>20</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="183" ht="16.5" spans="1:3">
       <c r="A183" s="2" t="s">
         <v>18</v>
       </c>
@@ -2979,10 +3596,10 @@
         <v>21</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="184" ht="16.5" spans="1:3">
       <c r="A184" s="2" t="s">
         <v>18</v>
       </c>
@@ -2990,10 +3607,10 @@
         <v>22</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="185" ht="16.5" spans="1:3">
       <c r="A185" s="2" t="s">
         <v>18</v>
       </c>
@@ -3001,10 +3618,10 @@
         <v>23</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="186" ht="16.5" spans="1:3">
       <c r="A186" s="2" t="s">
         <v>18</v>
       </c>
@@ -3012,10 +3629,10 @@
         <v>24</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="187" ht="16.5" spans="1:3">
       <c r="A187" s="2" t="s">
         <v>18</v>
       </c>
@@ -3023,10 +3640,10 @@
         <v>25</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="188" ht="16.5" spans="1:3">
       <c r="A188" s="2" t="s">
         <v>18</v>
       </c>
@@ -3034,10 +3651,10 @@
         <v>26</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="189" ht="16.5" spans="1:3">
       <c r="A189" s="2" t="s">
         <v>18</v>
       </c>
@@ -3045,10 +3662,10 @@
         <v>27</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="190" ht="16.5" spans="1:3">
       <c r="A190" s="2" t="s">
         <v>18</v>
       </c>
@@ -3056,10 +3673,10 @@
         <v>28</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="191" ht="16.5" spans="1:3">
       <c r="A191" s="2" t="s">
         <v>18</v>
       </c>
@@ -3067,10 +3684,10 @@
         <v>29</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="192" ht="16.5" spans="1:3">
       <c r="A192" s="2" t="s">
         <v>20</v>
       </c>
@@ -3078,10 +3695,10 @@
         <v>1</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="193" ht="16.5" spans="1:3">
       <c r="A193" s="2" t="s">
         <v>20</v>
       </c>
@@ -3089,10 +3706,10 @@
         <v>2</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="194" ht="16.5" spans="1:3">
       <c r="A194" s="2" t="s">
         <v>20</v>
       </c>
@@ -3100,10 +3717,10 @@
         <v>3</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="195" ht="16.5" spans="1:3">
       <c r="A195" s="2" t="s">
         <v>20</v>
       </c>
@@ -3111,10 +3728,10 @@
         <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="196" ht="16.5" spans="1:3">
       <c r="A196" s="2" t="s">
         <v>20</v>
       </c>
@@ -3122,10 +3739,10 @@
         <v>5</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="197" ht="16.5" spans="1:3">
       <c r="A197" s="2" t="s">
         <v>20</v>
       </c>
@@ -3133,10 +3750,10 @@
         <v>6</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="198" ht="16.5" spans="1:3">
       <c r="A198" s="2" t="s">
         <v>20</v>
       </c>
@@ -3144,10 +3761,10 @@
         <v>7</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="199" ht="16.5" spans="1:3">
       <c r="A199" s="2" t="s">
         <v>20</v>
       </c>
@@ -3155,10 +3772,10 @@
         <v>8</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="200" ht="16.5" spans="1:3">
       <c r="A200" s="2" t="s">
         <v>20</v>
       </c>
@@ -3166,10 +3783,10 @@
         <v>9</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="201" ht="16.5" spans="1:3">
       <c r="A201" s="2" t="s">
         <v>20</v>
       </c>
@@ -3177,10 +3794,10 @@
         <v>10</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="202" ht="16.5" spans="1:3">
       <c r="A202" s="2" t="s">
         <v>20</v>
       </c>
@@ -3188,10 +3805,10 @@
         <v>11</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="203" ht="16.5" spans="1:3">
       <c r="A203" s="2" t="s">
         <v>20</v>
       </c>
@@ -3199,10 +3816,10 @@
         <v>12</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="204" ht="16.5" spans="1:3">
       <c r="A204" s="2" t="s">
         <v>20</v>
       </c>
@@ -3210,10 +3827,10 @@
         <v>13</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="205" ht="16.5" spans="1:3">
       <c r="A205" s="2" t="s">
         <v>20</v>
       </c>
@@ -3221,10 +3838,10 @@
         <v>14</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="206" ht="16.5" spans="1:3">
       <c r="A206" s="2" t="s">
         <v>20</v>
       </c>
@@ -3232,10 +3849,10 @@
         <v>15</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="207" ht="16.5" spans="1:3">
       <c r="A207" s="2" t="s">
         <v>20</v>
       </c>
@@ -3243,10 +3860,10 @@
         <v>16</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="208" ht="16.5" spans="1:3">
       <c r="A208" s="2" t="s">
         <v>20</v>
       </c>
@@ -3254,10 +3871,10 @@
         <v>17</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="209" ht="16.5" spans="1:3">
       <c r="A209" s="2" t="s">
         <v>20</v>
       </c>
@@ -3265,10 +3882,10 @@
         <v>18</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="210" ht="16.5" spans="1:3">
       <c r="A210" s="2" t="s">
         <v>20</v>
       </c>
@@ -3276,10 +3893,10 @@
         <v>19</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="211" ht="16.5" spans="1:3">
       <c r="A211" s="2" t="s">
         <v>20</v>
       </c>
@@ -3287,10 +3904,10 @@
         <v>20</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="212" ht="16.5" spans="1:3">
       <c r="A212" s="2" t="s">
         <v>20</v>
       </c>
@@ -3298,10 +3915,10 @@
         <v>21</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="213" ht="16.5" spans="1:3">
       <c r="A213" s="2" t="s">
         <v>20</v>
       </c>
@@ -3309,10 +3926,10 @@
         <v>22</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="214" ht="16.5" spans="1:3">
       <c r="A214" s="2" t="s">
         <v>20</v>
       </c>
@@ -3320,10 +3937,10 @@
         <v>23</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="215" ht="16.5" spans="1:3">
       <c r="A215" s="2" t="s">
         <v>20</v>
       </c>
@@ -3331,10 +3948,10 @@
         <v>24</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="216" ht="16.5" spans="1:3">
       <c r="A216" s="2" t="s">
         <v>20</v>
       </c>
@@ -3342,10 +3959,10 @@
         <v>25</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="217" ht="16.5" spans="1:3">
       <c r="A217" s="2" t="s">
         <v>21</v>
       </c>
@@ -3353,10 +3970,10 @@
         <v>1</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="218" ht="16.5" spans="1:3">
       <c r="A218" s="2" t="s">
         <v>21</v>
       </c>
@@ -3364,10 +3981,10 @@
         <v>2</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="219" ht="16.5" spans="1:3">
       <c r="A219" s="2" t="s">
         <v>21</v>
       </c>
@@ -3375,10 +3992,10 @@
         <v>3</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="220" ht="16.5" spans="1:3">
       <c r="A220" s="2" t="s">
         <v>21</v>
       </c>
@@ -3386,10 +4003,10 @@
         <v>4</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="221" ht="16.5" spans="1:3">
       <c r="A221" s="2" t="s">
         <v>21</v>
       </c>
@@ -3397,10 +4014,10 @@
         <v>5</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="222" ht="16.5" spans="1:3">
       <c r="A222" s="2" t="s">
         <v>21</v>
       </c>
@@ -3408,10 +4025,10 @@
         <v>6</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="223" ht="16.5" spans="1:3">
       <c r="A223" s="2" t="s">
         <v>21</v>
       </c>
@@ -3419,10 +4036,10 @@
         <v>7</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="224" ht="16.5" spans="1:3">
       <c r="A224" s="2" t="s">
         <v>21</v>
       </c>
@@ -3430,10 +4047,10 @@
         <v>8</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="225" ht="16.5" spans="1:3">
       <c r="A225" s="2" t="s">
         <v>21</v>
       </c>
@@ -3441,10 +4058,10 @@
         <v>9</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="226" ht="16.5" spans="1:3">
       <c r="A226" s="2" t="s">
         <v>21</v>
       </c>
@@ -3452,10 +4069,10 @@
         <v>10</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="227" ht="16.5" spans="1:3">
       <c r="A227" s="2" t="s">
         <v>21</v>
       </c>
@@ -3463,10 +4080,10 @@
         <v>11</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="228" ht="16.5" spans="1:3">
       <c r="A228" s="2" t="s">
         <v>21</v>
       </c>
@@ -3474,10 +4091,10 @@
         <v>12</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="229" ht="16.5" spans="1:3">
       <c r="A229" s="2" t="s">
         <v>21</v>
       </c>
@@ -3485,10 +4102,10 @@
         <v>13</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="230" ht="16.5" spans="1:3">
       <c r="A230" s="2" t="s">
         <v>21</v>
       </c>
@@ -3496,10 +4113,10 @@
         <v>14</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="231" ht="16.5" spans="1:3">
       <c r="A231" s="2" t="s">
         <v>21</v>
       </c>
@@ -3507,10 +4124,10 @@
         <v>15</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="232" ht="16.5" spans="1:3">
       <c r="A232" s="2" t="s">
         <v>21</v>
       </c>
@@ -3518,10 +4135,10 @@
         <v>16</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="233" ht="16.5" spans="1:3">
       <c r="A233" s="2" t="s">
         <v>21</v>
       </c>
@@ -3529,10 +4146,10 @@
         <v>17</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="234" ht="16.5" spans="1:3">
       <c r="A234" s="2" t="s">
         <v>21</v>
       </c>
@@ -3540,10 +4157,10 @@
         <v>18</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="235" ht="16.5" spans="1:3">
       <c r="A235" s="2" t="s">
         <v>21</v>
       </c>
@@ -3551,10 +4168,10 @@
         <v>19</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="236" ht="16.5" spans="1:3">
       <c r="A236" s="2" t="s">
         <v>21</v>
       </c>
@@ -3562,10 +4179,10 @@
         <v>20</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="237" ht="16.5" spans="1:3">
       <c r="A237" s="2" t="s">
         <v>21</v>
       </c>
@@ -3573,10 +4190,10 @@
         <v>21</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="238" ht="16.5" spans="1:3">
       <c r="A238" s="2" t="s">
         <v>21</v>
       </c>
@@ -3584,10 +4201,10 @@
         <v>22</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="239" ht="16.5" spans="1:3">
       <c r="A239" s="2" t="s">
         <v>21</v>
       </c>
@@ -3595,10 +4212,10 @@
         <v>23</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="240" ht="16.5" spans="1:3">
       <c r="A240" s="2" t="s">
         <v>23</v>
       </c>
@@ -3606,10 +4223,10 @@
         <v>1</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="241" ht="16.5" spans="1:3">
       <c r="A241" s="2" t="s">
         <v>23</v>
       </c>
@@ -3617,10 +4234,10 @@
         <v>2</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="242" ht="16.5" spans="1:3">
       <c r="A242" s="2" t="s">
         <v>23</v>
       </c>
@@ -3628,10 +4245,10 @@
         <v>3</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="243" ht="16.5" spans="1:3">
       <c r="A243" s="2" t="s">
         <v>23</v>
       </c>
@@ -3639,10 +4256,10 @@
         <v>4</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="244" ht="16.5" spans="1:3">
       <c r="A244" s="2" t="s">
         <v>23</v>
       </c>
@@ -3650,10 +4267,10 @@
         <v>5</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="245" ht="16.5" spans="1:3">
       <c r="A245" s="2" t="s">
         <v>23</v>
       </c>
@@ -3661,10 +4278,10 @@
         <v>6</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="246" ht="16.5" spans="1:3">
       <c r="A246" s="2" t="s">
         <v>23</v>
       </c>
@@ -3672,10 +4289,10 @@
         <v>7</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="247" ht="16.5" spans="1:3">
       <c r="A247" s="2" t="s">
         <v>23</v>
       </c>
@@ -3683,10 +4300,10 @@
         <v>8</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="248" ht="16.5" spans="1:3">
       <c r="A248" s="2" t="s">
         <v>23</v>
       </c>
@@ -3694,10 +4311,10 @@
         <v>9</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="249" ht="16.5" spans="1:3">
       <c r="A249" s="2" t="s">
         <v>23</v>
       </c>
@@ -3705,10 +4322,10 @@
         <v>10</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="250" ht="16.5" spans="1:3">
       <c r="A250" s="2" t="s">
         <v>23</v>
       </c>
@@ -3716,10 +4333,10 @@
         <v>11</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="251" ht="16.5" spans="1:3">
       <c r="A251" s="2" t="s">
         <v>23</v>
       </c>
@@ -3727,10 +4344,10 @@
         <v>12</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="252" ht="16.5" spans="1:3">
       <c r="A252" s="2" t="s">
         <v>23</v>
       </c>
@@ -3738,10 +4355,10 @@
         <v>13</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="253" ht="16.5" spans="1:3">
       <c r="A253" s="2" t="s">
         <v>23</v>
       </c>
@@ -3749,10 +4366,10 @@
         <v>14</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="254" ht="16.5" spans="1:3">
       <c r="A254" s="2" t="s">
         <v>23</v>
       </c>
@@ -3760,10 +4377,10 @@
         <v>15</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="255" ht="16.5" spans="1:3">
       <c r="A255" s="2" t="s">
         <v>23</v>
       </c>
@@ -3771,10 +4388,10 @@
         <v>16</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="256" ht="16.5" spans="1:3">
       <c r="A256" s="2" t="s">
         <v>23</v>
       </c>
@@ -3782,10 +4399,10 @@
         <v>17</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="257" ht="16.5" spans="1:3">
       <c r="A257" s="2" t="s">
         <v>23</v>
       </c>
@@ -3793,10 +4410,10 @@
         <v>18</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="258" ht="16.5" spans="1:3">
       <c r="A258" s="2" t="s">
         <v>23</v>
       </c>
@@ -3804,10 +4421,10 @@
         <v>19</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="259" ht="16.5" spans="1:3">
       <c r="A259" s="2" t="s">
         <v>23</v>
       </c>
@@ -3815,10 +4432,10 @@
         <v>20</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="260" ht="16.5" spans="1:3">
       <c r="A260" s="2" t="s">
         <v>23</v>
       </c>
@@ -3826,10 +4443,10 @@
         <v>21</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="261" ht="16.5" spans="1:3">
       <c r="A261" s="2" t="s">
         <v>23</v>
       </c>
@@ -3837,10 +4454,10 @@
         <v>22</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="262" ht="16.5" spans="1:3">
       <c r="A262" s="2" t="s">
         <v>23</v>
       </c>
@@ -3848,10 +4465,10 @@
         <v>23</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="263" ht="16.5" spans="1:3">
       <c r="A263" s="2" t="s">
         <v>23</v>
       </c>
@@ -3859,10 +4476,10 @@
         <v>24</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="264" ht="16.5" spans="1:3">
       <c r="A264" s="2" t="s">
         <v>23</v>
       </c>
@@ -3870,10 +4487,10 @@
         <v>25</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" ht="29.15" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="265" ht="16.5" spans="1:3">
       <c r="A265" s="2" t="s">
         <v>23</v>
       </c>
@@ -3881,10 +4498,10 @@
         <v>26</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" ht="14.6" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="266" ht="16.5" spans="1:3">
       <c r="A266" s="2" t="s">
         <v>23</v>
       </c>
@@ -3892,41 +4509,44 @@
         <v>27</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E990B59-5726-486C-A861-53C88AA76BA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="5" width="9.140625" style="3"/>
+    <col min="1" max="3" width="17.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="49.5" spans="1:5">
+      <c r="A1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="2" ht="33" spans="1:5">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -3943,7 +4563,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -3960,7 +4580,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="4" ht="16.5" spans="1:5">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -3977,7 +4597,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="5" ht="16.5" spans="1:5">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -3994,7 +4614,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="6" ht="16.5" spans="1:5">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -4011,7 +4631,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="7" ht="16.5" spans="1:5">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -4028,7 +4648,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -4045,7 +4665,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="9" ht="16.5" spans="1:5">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -4062,7 +4682,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="10" ht="16.5" spans="1:5">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -4079,7 +4699,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="11" ht="16.5" spans="1:5">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -4096,7 +4716,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="12" ht="16.5" spans="1:5">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -4113,7 +4733,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="13" ht="16.5" spans="1:5">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -4130,7 +4750,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="14" ht="16.5" spans="1:5">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -4147,7 +4767,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="14.6" x14ac:dyDescent="0.35">
+    <row r="15" ht="16.5" spans="1:5">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -4165,7 +4785,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>